--- a/simple_game_test/corrected_combined_metrics_analysis.xlsx
+++ b/simple_game_test/corrected_combined_metrics_analysis.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q173"/>
+  <dimension ref="A1:S173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -514,6 +514,16 @@
           <t>individuals_unlearned</t>
         </is>
       </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>groups_learned</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>groups_unlearned</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -565,12 +575,18 @@
         <v>8</v>
       </c>
       <c r="O2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P2" t="b">
         <v>1</v>
       </c>
       <c r="Q2" t="b">
+        <v>1</v>
+      </c>
+      <c r="R2" t="b">
+        <v>0</v>
+      </c>
+      <c r="S2" t="b">
         <v>1</v>
       </c>
     </row>
@@ -624,12 +640,18 @@
         <v>8</v>
       </c>
       <c r="O3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P3" t="b">
         <v>0</v>
       </c>
       <c r="Q3" t="b">
+        <v>0</v>
+      </c>
+      <c r="R3" t="b">
+        <v>0</v>
+      </c>
+      <c r="S3" t="b">
         <v>1</v>
       </c>
     </row>
@@ -683,13 +705,19 @@
         <v>7</v>
       </c>
       <c r="O4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="b">
         <v>0</v>
+      </c>
+      <c r="R4" t="b">
+        <v>0</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -742,12 +770,18 @@
         <v>8</v>
       </c>
       <c r="O5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P5" t="b">
         <v>0</v>
       </c>
       <c r="Q5" t="b">
+        <v>0</v>
+      </c>
+      <c r="R5" t="b">
+        <v>0</v>
+      </c>
+      <c r="S5" t="b">
         <v>1</v>
       </c>
     </row>
@@ -801,12 +835,18 @@
         <v>8</v>
       </c>
       <c r="O6" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="P6" t="b">
         <v>0</v>
       </c>
       <c r="Q6" t="b">
+        <v>0</v>
+      </c>
+      <c r="R6" t="b">
+        <v>0</v>
+      </c>
+      <c r="S6" t="b">
         <v>0</v>
       </c>
     </row>
@@ -860,13 +900,19 @@
         <v>9</v>
       </c>
       <c r="O7" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="P7" t="b">
         <v>0</v>
       </c>
       <c r="Q7" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R7" t="b">
+        <v>0</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -919,13 +965,19 @@
         <v>8</v>
       </c>
       <c r="O8" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="P8" t="b">
         <v>0</v>
       </c>
       <c r="Q8" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R8" t="b">
+        <v>0</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -978,12 +1030,18 @@
         <v>9</v>
       </c>
       <c r="O9" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="P9" t="b">
         <v>0</v>
       </c>
       <c r="Q9" t="b">
+        <v>0</v>
+      </c>
+      <c r="R9" t="b">
+        <v>0</v>
+      </c>
+      <c r="S9" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1037,12 +1095,18 @@
         <v>7</v>
       </c>
       <c r="O10" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P10" t="b">
         <v>1</v>
       </c>
       <c r="Q10" t="b">
+        <v>0</v>
+      </c>
+      <c r="R10" t="b">
+        <v>0</v>
+      </c>
+      <c r="S10" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1104,6 +1168,12 @@
       <c r="Q11" t="b">
         <v>0</v>
       </c>
+      <c r="R11" t="b">
+        <v>0</v>
+      </c>
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1155,13 +1225,19 @@
         <v>7</v>
       </c>
       <c r="O12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P12" t="b">
         <v>0</v>
       </c>
       <c r="Q12" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R12" t="b">
+        <v>0</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1222,6 +1298,12 @@
       <c r="Q13" t="b">
         <v>0</v>
       </c>
+      <c r="R13" t="b">
+        <v>0</v>
+      </c>
+      <c r="S13" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1273,12 +1355,18 @@
         <v>7</v>
       </c>
       <c r="O14" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P14" t="b">
         <v>0</v>
       </c>
       <c r="Q14" t="b">
+        <v>0</v>
+      </c>
+      <c r="R14" t="b">
+        <v>0</v>
+      </c>
+      <c r="S14" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1340,6 +1428,12 @@
       <c r="Q15" t="b">
         <v>0</v>
       </c>
+      <c r="R15" t="b">
+        <v>0</v>
+      </c>
+      <c r="S15" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1391,13 +1485,19 @@
         <v>7</v>
       </c>
       <c r="O16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P16" t="b">
         <v>1</v>
       </c>
       <c r="Q16" t="b">
         <v>0</v>
+      </c>
+      <c r="R16" t="b">
+        <v>0</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1450,12 +1550,18 @@
         <v>10</v>
       </c>
       <c r="O17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P17" t="b">
         <v>0</v>
       </c>
       <c r="Q17" t="b">
+        <v>0</v>
+      </c>
+      <c r="R17" t="b">
+        <v>0</v>
+      </c>
+      <c r="S17" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1509,12 +1615,18 @@
         <v>3</v>
       </c>
       <c r="O18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P18" t="b">
         <v>1</v>
       </c>
       <c r="Q18" t="b">
+        <v>0</v>
+      </c>
+      <c r="R18" t="b">
+        <v>1</v>
+      </c>
+      <c r="S18" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1568,13 +1680,19 @@
         <v>7</v>
       </c>
       <c r="O19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P19" t="b">
         <v>1</v>
       </c>
       <c r="Q19" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R19" t="b">
+        <v>0</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1635,6 +1753,12 @@
       <c r="Q20" t="b">
         <v>0</v>
       </c>
+      <c r="R20" t="b">
+        <v>0</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1686,12 +1810,18 @@
         <v>6</v>
       </c>
       <c r="O21" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P21" t="b">
         <v>1</v>
       </c>
       <c r="Q21" t="b">
+        <v>0</v>
+      </c>
+      <c r="R21" t="b">
+        <v>1</v>
+      </c>
+      <c r="S21" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1745,12 +1875,18 @@
         <v>7</v>
       </c>
       <c r="O22" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q22" t="b">
+        <v>1</v>
+      </c>
+      <c r="R22" t="b">
+        <v>0</v>
+      </c>
+      <c r="S22" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1804,12 +1940,18 @@
         <v>7</v>
       </c>
       <c r="O23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P23" t="b">
         <v>1</v>
       </c>
       <c r="Q23" t="b">
+        <v>1</v>
+      </c>
+      <c r="R23" t="b">
+        <v>0</v>
+      </c>
+      <c r="S23" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1863,13 +2005,19 @@
         <v>10</v>
       </c>
       <c r="O24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P24" t="b">
         <v>1</v>
       </c>
       <c r="Q24" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R24" t="b">
+        <v>0</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1922,12 +2070,18 @@
         <v>3</v>
       </c>
       <c r="O25" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P25" t="b">
         <v>1</v>
       </c>
       <c r="Q25" t="b">
+        <v>0</v>
+      </c>
+      <c r="R25" t="b">
+        <v>1</v>
+      </c>
+      <c r="S25" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1981,12 +2135,18 @@
         <v>7</v>
       </c>
       <c r="O26" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P26" t="b">
         <v>1</v>
       </c>
       <c r="Q26" t="b">
+        <v>0</v>
+      </c>
+      <c r="R26" t="b">
+        <v>0</v>
+      </c>
+      <c r="S26" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2040,12 +2200,18 @@
         <v>6</v>
       </c>
       <c r="O27" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q27" t="b">
+        <v>0</v>
+      </c>
+      <c r="R27" t="b">
+        <v>1</v>
+      </c>
+      <c r="S27" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2099,13 +2265,19 @@
         <v>7</v>
       </c>
       <c r="O28" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P28" t="b">
         <v>0</v>
       </c>
       <c r="Q28" t="b">
         <v>0</v>
+      </c>
+      <c r="R28" t="b">
+        <v>0</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2166,6 +2338,12 @@
       <c r="Q29" t="b">
         <v>0</v>
       </c>
+      <c r="R29" t="b">
+        <v>0</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2225,6 +2403,12 @@
       <c r="Q30" t="b">
         <v>0</v>
       </c>
+      <c r="R30" t="b">
+        <v>0</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2276,12 +2460,18 @@
         <v>9</v>
       </c>
       <c r="O31" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="P31" t="b">
         <v>0</v>
       </c>
       <c r="Q31" t="b">
+        <v>0</v>
+      </c>
+      <c r="R31" t="b">
+        <v>0</v>
+      </c>
+      <c r="S31" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2335,12 +2525,18 @@
         <v>10</v>
       </c>
       <c r="O32" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="P32" t="b">
         <v>0</v>
       </c>
       <c r="Q32" t="b">
+        <v>0</v>
+      </c>
+      <c r="R32" t="b">
+        <v>0</v>
+      </c>
+      <c r="S32" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2394,12 +2590,18 @@
         <v>9</v>
       </c>
       <c r="O33" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="P33" t="b">
         <v>0</v>
       </c>
       <c r="Q33" t="b">
+        <v>0</v>
+      </c>
+      <c r="R33" t="b">
+        <v>0</v>
+      </c>
+      <c r="S33" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2453,12 +2655,18 @@
         <v>10</v>
       </c>
       <c r="O34" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="P34" t="b">
         <v>1</v>
       </c>
       <c r="Q34" t="b">
+        <v>0</v>
+      </c>
+      <c r="R34" t="b">
+        <v>0</v>
+      </c>
+      <c r="S34" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2520,6 +2728,12 @@
       <c r="Q35" t="b">
         <v>1</v>
       </c>
+      <c r="R35" t="b">
+        <v>0</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2571,13 +2785,19 @@
         <v>6</v>
       </c>
       <c r="O36" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P36" t="b">
         <v>0</v>
       </c>
       <c r="Q36" t="b">
         <v>0</v>
+      </c>
+      <c r="R36" t="b">
+        <v>0</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2638,6 +2858,12 @@
       <c r="Q37" t="b">
         <v>0</v>
       </c>
+      <c r="R37" t="b">
+        <v>0</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2689,12 +2915,18 @@
         <v>6</v>
       </c>
       <c r="O38" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P38" t="b">
         <v>1</v>
       </c>
       <c r="Q38" t="b">
+        <v>1</v>
+      </c>
+      <c r="R38" t="b">
+        <v>0</v>
+      </c>
+      <c r="S38" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2756,6 +2988,12 @@
       <c r="Q39" t="b">
         <v>0</v>
       </c>
+      <c r="R39" t="b">
+        <v>0</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2807,12 +3045,18 @@
         <v>10</v>
       </c>
       <c r="O40" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="P40" t="b">
         <v>0</v>
       </c>
       <c r="Q40" t="b">
+        <v>0</v>
+      </c>
+      <c r="R40" t="b">
+        <v>0</v>
+      </c>
+      <c r="S40" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2866,12 +3110,18 @@
         <v>9</v>
       </c>
       <c r="O41" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="P41" t="b">
         <v>0</v>
       </c>
       <c r="Q41" t="b">
+        <v>1</v>
+      </c>
+      <c r="R41" t="b">
+        <v>0</v>
+      </c>
+      <c r="S41" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2925,12 +3175,18 @@
         <v>10</v>
       </c>
       <c r="O42" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="P42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q42" t="b">
+        <v>1</v>
+      </c>
+      <c r="R42" t="b">
+        <v>0</v>
+      </c>
+      <c r="S42" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2984,13 +3240,19 @@
         <v>9</v>
       </c>
       <c r="O43" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="P43" t="b">
         <v>0</v>
       </c>
       <c r="Q43" t="b">
         <v>0</v>
+      </c>
+      <c r="R43" t="b">
+        <v>0</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -3051,6 +3313,12 @@
       <c r="Q44" t="b">
         <v>0</v>
       </c>
+      <c r="R44" t="b">
+        <v>0</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -3110,6 +3378,12 @@
       <c r="Q45" t="b">
         <v>0</v>
       </c>
+      <c r="R45" t="b">
+        <v>0</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -3161,12 +3435,18 @@
         <v>10</v>
       </c>
       <c r="O46" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P46" t="b">
         <v>1</v>
       </c>
       <c r="Q46" t="b">
+        <v>0</v>
+      </c>
+      <c r="R46" t="b">
+        <v>0</v>
+      </c>
+      <c r="S46" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3220,12 +3500,18 @@
         <v>10</v>
       </c>
       <c r="O47" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P47" t="b">
         <v>0</v>
       </c>
       <c r="Q47" t="b">
+        <v>0</v>
+      </c>
+      <c r="R47" t="b">
+        <v>0</v>
+      </c>
+      <c r="S47" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3279,13 +3565,19 @@
         <v>10</v>
       </c>
       <c r="O48" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P48" t="b">
         <v>0</v>
       </c>
       <c r="Q48" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R48" t="b">
+        <v>0</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3338,12 +3630,18 @@
         <v>10</v>
       </c>
       <c r="O49" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P49" t="b">
         <v>0</v>
       </c>
       <c r="Q49" t="b">
+        <v>0</v>
+      </c>
+      <c r="R49" t="b">
+        <v>0</v>
+      </c>
+      <c r="S49" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3397,12 +3695,18 @@
         <v>9</v>
       </c>
       <c r="O50" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="P50" t="b">
         <v>0</v>
       </c>
       <c r="Q50" t="b">
+        <v>0</v>
+      </c>
+      <c r="R50" t="b">
+        <v>0</v>
+      </c>
+      <c r="S50" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3456,12 +3760,18 @@
         <v>10</v>
       </c>
       <c r="O51" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="P51" t="b">
         <v>0</v>
       </c>
       <c r="Q51" t="b">
+        <v>0</v>
+      </c>
+      <c r="R51" t="b">
+        <v>0</v>
+      </c>
+      <c r="S51" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3515,12 +3825,18 @@
         <v>9</v>
       </c>
       <c r="O52" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="P52" t="b">
         <v>0</v>
       </c>
       <c r="Q52" t="b">
+        <v>0</v>
+      </c>
+      <c r="R52" t="b">
+        <v>0</v>
+      </c>
+      <c r="S52" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3574,13 +3890,19 @@
         <v>10</v>
       </c>
       <c r="O53" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="P53" t="b">
         <v>0</v>
       </c>
       <c r="Q53" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R53" t="b">
+        <v>0</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3633,12 +3955,18 @@
         <v>9</v>
       </c>
       <c r="O54" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="P54" t="b">
         <v>1</v>
       </c>
       <c r="Q54" t="b">
+        <v>0</v>
+      </c>
+      <c r="R54" t="b">
+        <v>0</v>
+      </c>
+      <c r="S54" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3692,12 +4020,18 @@
         <v>10</v>
       </c>
       <c r="O55" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="P55" t="b">
         <v>0</v>
       </c>
       <c r="Q55" t="b">
+        <v>0</v>
+      </c>
+      <c r="R55" t="b">
+        <v>0</v>
+      </c>
+      <c r="S55" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3751,13 +4085,19 @@
         <v>7</v>
       </c>
       <c r="O56" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q56" t="b">
         <v>0</v>
+      </c>
+      <c r="R56" t="b">
+        <v>1</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3810,13 +4150,19 @@
         <v>9</v>
       </c>
       <c r="O57" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P57" t="b">
         <v>0</v>
       </c>
       <c r="Q57" t="b">
         <v>0</v>
+      </c>
+      <c r="R57" t="b">
+        <v>0</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3869,12 +4215,18 @@
         <v>9</v>
       </c>
       <c r="O58" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="P58" t="b">
         <v>0</v>
       </c>
       <c r="Q58" t="b">
+        <v>0</v>
+      </c>
+      <c r="R58" t="b">
+        <v>0</v>
+      </c>
+      <c r="S58" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3928,13 +4280,19 @@
         <v>7</v>
       </c>
       <c r="O59" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="P59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q59" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R59" t="b">
+        <v>1</v>
+      </c>
+      <c r="S59" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3987,12 +4345,18 @@
         <v>7</v>
       </c>
       <c r="O60" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P60" t="b">
         <v>1</v>
       </c>
       <c r="Q60" t="b">
+        <v>1</v>
+      </c>
+      <c r="R60" t="b">
+        <v>1</v>
+      </c>
+      <c r="S60" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4046,12 +4410,18 @@
         <v>9</v>
       </c>
       <c r="O61" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P61" t="b">
         <v>1</v>
       </c>
       <c r="Q61" t="b">
+        <v>1</v>
+      </c>
+      <c r="R61" t="b">
+        <v>0</v>
+      </c>
+      <c r="S61" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4105,12 +4475,18 @@
         <v>7</v>
       </c>
       <c r="O62" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P62" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q62" t="b">
+        <v>0</v>
+      </c>
+      <c r="R62" t="b">
+        <v>1</v>
+      </c>
+      <c r="S62" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4164,12 +4540,18 @@
         <v>10</v>
       </c>
       <c r="O63" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P63" t="b">
         <v>1</v>
       </c>
       <c r="Q63" t="b">
+        <v>0</v>
+      </c>
+      <c r="R63" t="b">
+        <v>0</v>
+      </c>
+      <c r="S63" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4223,12 +4605,18 @@
         <v>7</v>
       </c>
       <c r="O64" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P64" t="b">
         <v>1</v>
       </c>
       <c r="Q64" t="b">
+        <v>0</v>
+      </c>
+      <c r="R64" t="b">
+        <v>1</v>
+      </c>
+      <c r="S64" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4282,12 +4670,18 @@
         <v>10</v>
       </c>
       <c r="O65" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P65" t="b">
         <v>0</v>
       </c>
       <c r="Q65" t="b">
+        <v>0</v>
+      </c>
+      <c r="R65" t="b">
+        <v>0</v>
+      </c>
+      <c r="S65" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4341,12 +4735,18 @@
         <v>7</v>
       </c>
       <c r="O66" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q66" t="b">
+        <v>0</v>
+      </c>
+      <c r="R66" t="b">
+        <v>1</v>
+      </c>
+      <c r="S66" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4400,12 +4800,18 @@
         <v>10</v>
       </c>
       <c r="O67" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P67" t="b">
         <v>0</v>
       </c>
       <c r="Q67" t="b">
+        <v>0</v>
+      </c>
+      <c r="R67" t="b">
+        <v>0</v>
+      </c>
+      <c r="S67" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4459,13 +4865,19 @@
         <v>9</v>
       </c>
       <c r="O68" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="P68" t="b">
         <v>0</v>
       </c>
       <c r="Q68" t="b">
         <v>0</v>
+      </c>
+      <c r="R68" t="b">
+        <v>0</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4518,12 +4930,18 @@
         <v>9</v>
       </c>
       <c r="O69" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="P69" t="b">
         <v>0</v>
       </c>
       <c r="Q69" t="b">
+        <v>0</v>
+      </c>
+      <c r="R69" t="b">
+        <v>0</v>
+      </c>
+      <c r="S69" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4577,13 +4995,19 @@
         <v>9</v>
       </c>
       <c r="O70" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="P70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q70" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R70" t="b">
+        <v>0</v>
+      </c>
+      <c r="S70" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -4636,13 +5060,19 @@
         <v>7</v>
       </c>
       <c r="O71" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="P71" t="b">
         <v>1</v>
       </c>
       <c r="Q71" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R71" t="b">
+        <v>1</v>
+      </c>
+      <c r="S71" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -4695,13 +5125,19 @@
         <v>9</v>
       </c>
       <c r="O72" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="P72" t="b">
         <v>1</v>
       </c>
       <c r="Q72" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R72" t="b">
+        <v>0</v>
+      </c>
+      <c r="S72" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -4754,13 +5190,19 @@
         <v>9</v>
       </c>
       <c r="O73" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="P73" t="b">
         <v>0</v>
       </c>
       <c r="Q73" t="b">
         <v>0</v>
+      </c>
+      <c r="R73" t="b">
+        <v>0</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -4813,13 +5255,19 @@
         <v>9</v>
       </c>
       <c r="O74" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="P74" t="b">
         <v>0</v>
       </c>
       <c r="Q74" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R74" t="b">
+        <v>0</v>
+      </c>
+      <c r="S74" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -4880,6 +5328,12 @@
       <c r="Q75" t="b">
         <v>0</v>
       </c>
+      <c r="R75" t="b">
+        <v>0</v>
+      </c>
+      <c r="S75" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -4931,13 +5385,19 @@
         <v>9</v>
       </c>
       <c r="O76" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="P76" t="b">
         <v>0</v>
       </c>
       <c r="Q76" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R76" t="b">
+        <v>0</v>
+      </c>
+      <c r="S76" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -4990,13 +5450,19 @@
         <v>9</v>
       </c>
       <c r="O77" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="P77" t="b">
         <v>0</v>
       </c>
       <c r="Q77" t="b">
         <v>0</v>
+      </c>
+      <c r="R77" t="b">
+        <v>0</v>
+      </c>
+      <c r="S77" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -5049,12 +5515,18 @@
         <v>3</v>
       </c>
       <c r="O78" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P78" t="b">
         <v>1</v>
       </c>
       <c r="Q78" t="b">
+        <v>0</v>
+      </c>
+      <c r="R78" t="b">
+        <v>1</v>
+      </c>
+      <c r="S78" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5116,6 +5588,12 @@
       <c r="Q79" t="b">
         <v>0</v>
       </c>
+      <c r="R79" t="b">
+        <v>0</v>
+      </c>
+      <c r="S79" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -5167,12 +5645,18 @@
         <v>9</v>
       </c>
       <c r="O80" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="P80" t="b">
         <v>0</v>
       </c>
       <c r="Q80" t="b">
+        <v>0</v>
+      </c>
+      <c r="R80" t="b">
+        <v>0</v>
+      </c>
+      <c r="S80" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5226,12 +5710,18 @@
         <v>9</v>
       </c>
       <c r="O81" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="P81" t="b">
         <v>0</v>
       </c>
       <c r="Q81" t="b">
+        <v>1</v>
+      </c>
+      <c r="R81" t="b">
+        <v>0</v>
+      </c>
+      <c r="S81" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5285,12 +5775,18 @@
         <v>3</v>
       </c>
       <c r="O82" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P82" t="b">
         <v>1</v>
       </c>
       <c r="Q82" t="b">
+        <v>0</v>
+      </c>
+      <c r="R82" t="b">
+        <v>1</v>
+      </c>
+      <c r="S82" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5352,6 +5848,12 @@
       <c r="Q83" t="b">
         <v>0</v>
       </c>
+      <c r="R83" t="b">
+        <v>0</v>
+      </c>
+      <c r="S83" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -5403,12 +5905,18 @@
         <v>11</v>
       </c>
       <c r="O84" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P84" t="b">
         <v>0</v>
       </c>
       <c r="Q84" t="b">
+        <v>1</v>
+      </c>
+      <c r="R84" t="b">
+        <v>0</v>
+      </c>
+      <c r="S84" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5462,13 +5970,19 @@
         <v>8</v>
       </c>
       <c r="O85" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="P85" t="b">
         <v>0</v>
       </c>
       <c r="Q85" t="b">
         <v>0</v>
+      </c>
+      <c r="R85" t="b">
+        <v>0</v>
+      </c>
+      <c r="S85" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="86">
@@ -5521,12 +6035,18 @@
         <v>3</v>
       </c>
       <c r="O86" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P86" t="b">
         <v>1</v>
       </c>
       <c r="Q86" t="b">
+        <v>0</v>
+      </c>
+      <c r="R86" t="b">
+        <v>1</v>
+      </c>
+      <c r="S86" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5586,7 +6106,13 @@
         <v>0</v>
       </c>
       <c r="Q87" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R87" t="b">
+        <v>0</v>
+      </c>
+      <c r="S87" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -5639,13 +6165,19 @@
         <v>11</v>
       </c>
       <c r="O88" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P88" t="b">
         <v>0</v>
       </c>
       <c r="Q88" t="b">
         <v>0</v>
+      </c>
+      <c r="R88" t="b">
+        <v>0</v>
+      </c>
+      <c r="S88" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="89">
@@ -5698,12 +6230,18 @@
         <v>8</v>
       </c>
       <c r="O89" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="P89" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q89" t="b">
+        <v>1</v>
+      </c>
+      <c r="R89" t="b">
+        <v>0</v>
+      </c>
+      <c r="S89" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5765,6 +6303,12 @@
       <c r="Q90" t="b">
         <v>1</v>
       </c>
+      <c r="R90" t="b">
+        <v>0</v>
+      </c>
+      <c r="S90" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -5824,6 +6368,12 @@
       <c r="Q91" t="b">
         <v>0</v>
       </c>
+      <c r="R91" t="b">
+        <v>0</v>
+      </c>
+      <c r="S91" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -5883,6 +6433,12 @@
       <c r="Q92" t="b">
         <v>0</v>
       </c>
+      <c r="R92" t="b">
+        <v>0</v>
+      </c>
+      <c r="S92" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -5942,6 +6498,12 @@
       <c r="Q93" t="b">
         <v>0</v>
       </c>
+      <c r="R93" t="b">
+        <v>0</v>
+      </c>
+      <c r="S93" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -6001,6 +6563,12 @@
       <c r="Q94" t="b">
         <v>1</v>
       </c>
+      <c r="R94" t="b">
+        <v>0</v>
+      </c>
+      <c r="S94" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -6060,6 +6628,12 @@
       <c r="Q95" t="b">
         <v>0</v>
       </c>
+      <c r="R95" t="b">
+        <v>0</v>
+      </c>
+      <c r="S95" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -6119,6 +6693,12 @@
       <c r="Q96" t="b">
         <v>0</v>
       </c>
+      <c r="R96" t="b">
+        <v>0</v>
+      </c>
+      <c r="S96" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -6178,6 +6758,12 @@
       <c r="Q97" t="b">
         <v>0</v>
       </c>
+      <c r="R97" t="b">
+        <v>0</v>
+      </c>
+      <c r="S97" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -6237,6 +6823,12 @@
       <c r="Q98" t="b">
         <v>0</v>
       </c>
+      <c r="R98" t="b">
+        <v>0</v>
+      </c>
+      <c r="S98" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -6296,6 +6888,12 @@
       <c r="Q99" t="b">
         <v>0</v>
       </c>
+      <c r="R99" t="b">
+        <v>0</v>
+      </c>
+      <c r="S99" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -6355,6 +6953,12 @@
       <c r="Q100" t="b">
         <v>0</v>
       </c>
+      <c r="R100" t="b">
+        <v>0</v>
+      </c>
+      <c r="S100" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -6414,6 +7018,12 @@
       <c r="Q101" t="b">
         <v>0</v>
       </c>
+      <c r="R101" t="b">
+        <v>0</v>
+      </c>
+      <c r="S101" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -6473,6 +7083,12 @@
       <c r="Q102" t="b">
         <v>0</v>
       </c>
+      <c r="R102" t="b">
+        <v>0</v>
+      </c>
+      <c r="S102" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -6532,6 +7148,12 @@
       <c r="Q103" t="b">
         <v>0</v>
       </c>
+      <c r="R103" t="b">
+        <v>0</v>
+      </c>
+      <c r="S103" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -6591,6 +7213,12 @@
       <c r="Q104" t="b">
         <v>0</v>
       </c>
+      <c r="R104" t="b">
+        <v>0</v>
+      </c>
+      <c r="S104" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -6650,6 +7278,12 @@
       <c r="Q105" t="b">
         <v>0</v>
       </c>
+      <c r="R105" t="b">
+        <v>0</v>
+      </c>
+      <c r="S105" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -6709,6 +7343,12 @@
       <c r="Q106" t="b">
         <v>0</v>
       </c>
+      <c r="R106" t="b">
+        <v>0</v>
+      </c>
+      <c r="S106" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -6768,6 +7408,12 @@
       <c r="Q107" t="b">
         <v>0</v>
       </c>
+      <c r="R107" t="b">
+        <v>0</v>
+      </c>
+      <c r="S107" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -6827,6 +7473,12 @@
       <c r="Q108" t="b">
         <v>0</v>
       </c>
+      <c r="R108" t="b">
+        <v>0</v>
+      </c>
+      <c r="S108" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -6886,6 +7538,12 @@
       <c r="Q109" t="b">
         <v>0</v>
       </c>
+      <c r="R109" t="b">
+        <v>0</v>
+      </c>
+      <c r="S109" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -6945,6 +7603,12 @@
       <c r="Q110" t="b">
         <v>0</v>
       </c>
+      <c r="R110" t="b">
+        <v>0</v>
+      </c>
+      <c r="S110" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -7004,6 +7668,12 @@
       <c r="Q111" t="b">
         <v>0</v>
       </c>
+      <c r="R111" t="b">
+        <v>0</v>
+      </c>
+      <c r="S111" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -7063,6 +7733,12 @@
       <c r="Q112" t="b">
         <v>0</v>
       </c>
+      <c r="R112" t="b">
+        <v>0</v>
+      </c>
+      <c r="S112" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -7122,6 +7798,12 @@
       <c r="Q113" t="b">
         <v>1</v>
       </c>
+      <c r="R113" t="b">
+        <v>0</v>
+      </c>
+      <c r="S113" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -7181,6 +7863,12 @@
       <c r="Q114" t="b">
         <v>1</v>
       </c>
+      <c r="R114" t="b">
+        <v>0</v>
+      </c>
+      <c r="S114" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -7240,6 +7928,12 @@
       <c r="Q115" t="b">
         <v>0</v>
       </c>
+      <c r="R115" t="b">
+        <v>0</v>
+      </c>
+      <c r="S115" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -7299,6 +7993,12 @@
       <c r="Q116" t="b">
         <v>0</v>
       </c>
+      <c r="R116" t="b">
+        <v>0</v>
+      </c>
+      <c r="S116" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -7358,6 +8058,12 @@
       <c r="Q117" t="b">
         <v>0</v>
       </c>
+      <c r="R117" t="b">
+        <v>0</v>
+      </c>
+      <c r="S117" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -7417,6 +8123,12 @@
       <c r="Q118" t="b">
         <v>0</v>
       </c>
+      <c r="R118" t="b">
+        <v>0</v>
+      </c>
+      <c r="S118" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -7476,6 +8188,12 @@
       <c r="Q119" t="b">
         <v>0</v>
       </c>
+      <c r="R119" t="b">
+        <v>0</v>
+      </c>
+      <c r="S119" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -7535,6 +8253,12 @@
       <c r="Q120" t="b">
         <v>0</v>
       </c>
+      <c r="R120" t="b">
+        <v>0</v>
+      </c>
+      <c r="S120" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -7594,6 +8318,12 @@
       <c r="Q121" t="b">
         <v>0</v>
       </c>
+      <c r="R121" t="b">
+        <v>0</v>
+      </c>
+      <c r="S121" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -7653,6 +8383,12 @@
       <c r="Q122" t="b">
         <v>0</v>
       </c>
+      <c r="R122" t="b">
+        <v>0</v>
+      </c>
+      <c r="S122" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -7712,6 +8448,12 @@
       <c r="Q123" t="b">
         <v>1</v>
       </c>
+      <c r="R123" t="b">
+        <v>0</v>
+      </c>
+      <c r="S123" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -7771,6 +8513,12 @@
       <c r="Q124" t="b">
         <v>1</v>
       </c>
+      <c r="R124" t="b">
+        <v>0</v>
+      </c>
+      <c r="S124" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -7830,6 +8578,12 @@
       <c r="Q125" t="b">
         <v>1</v>
       </c>
+      <c r="R125" t="b">
+        <v>0</v>
+      </c>
+      <c r="S125" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -7889,6 +8643,12 @@
       <c r="Q126" t="b">
         <v>0</v>
       </c>
+      <c r="R126" t="b">
+        <v>0</v>
+      </c>
+      <c r="S126" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -7948,6 +8708,12 @@
       <c r="Q127" t="b">
         <v>0</v>
       </c>
+      <c r="R127" t="b">
+        <v>0</v>
+      </c>
+      <c r="S127" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -8007,6 +8773,12 @@
       <c r="Q128" t="b">
         <v>0</v>
       </c>
+      <c r="R128" t="b">
+        <v>0</v>
+      </c>
+      <c r="S128" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -8066,6 +8838,12 @@
       <c r="Q129" t="b">
         <v>0</v>
       </c>
+      <c r="R129" t="b">
+        <v>0</v>
+      </c>
+      <c r="S129" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -8125,6 +8903,12 @@
       <c r="Q130" t="b">
         <v>0</v>
       </c>
+      <c r="R130" t="b">
+        <v>0</v>
+      </c>
+      <c r="S130" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -8184,6 +8968,12 @@
       <c r="Q131" t="b">
         <v>0</v>
       </c>
+      <c r="R131" t="b">
+        <v>0</v>
+      </c>
+      <c r="S131" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -8243,6 +9033,12 @@
       <c r="Q132" t="b">
         <v>0</v>
       </c>
+      <c r="R132" t="b">
+        <v>0</v>
+      </c>
+      <c r="S132" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -8302,6 +9098,12 @@
       <c r="Q133" t="b">
         <v>0</v>
       </c>
+      <c r="R133" t="b">
+        <v>0</v>
+      </c>
+      <c r="S133" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -8361,6 +9163,12 @@
       <c r="Q134" t="b">
         <v>0</v>
       </c>
+      <c r="R134" t="b">
+        <v>0</v>
+      </c>
+      <c r="S134" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -8420,6 +9228,12 @@
       <c r="Q135" t="b">
         <v>0</v>
       </c>
+      <c r="R135" t="b">
+        <v>0</v>
+      </c>
+      <c r="S135" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -8479,6 +9293,12 @@
       <c r="Q136" t="b">
         <v>0</v>
       </c>
+      <c r="R136" t="b">
+        <v>0</v>
+      </c>
+      <c r="S136" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -8538,6 +9358,12 @@
       <c r="Q137" t="b">
         <v>0</v>
       </c>
+      <c r="R137" t="b">
+        <v>0</v>
+      </c>
+      <c r="S137" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -8597,6 +9423,12 @@
       <c r="Q138" t="b">
         <v>0</v>
       </c>
+      <c r="R138" t="b">
+        <v>0</v>
+      </c>
+      <c r="S138" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -8656,6 +9488,12 @@
       <c r="Q139" t="b">
         <v>0</v>
       </c>
+      <c r="R139" t="b">
+        <v>0</v>
+      </c>
+      <c r="S139" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -8715,6 +9553,12 @@
       <c r="Q140" t="b">
         <v>0</v>
       </c>
+      <c r="R140" t="b">
+        <v>0</v>
+      </c>
+      <c r="S140" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -8774,6 +9618,12 @@
       <c r="Q141" t="b">
         <v>0</v>
       </c>
+      <c r="R141" t="b">
+        <v>0</v>
+      </c>
+      <c r="S141" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -8833,6 +9683,12 @@
       <c r="Q142" t="b">
         <v>1</v>
       </c>
+      <c r="R142" t="b">
+        <v>0</v>
+      </c>
+      <c r="S142" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -8892,6 +9748,12 @@
       <c r="Q143" t="b">
         <v>0</v>
       </c>
+      <c r="R143" t="b">
+        <v>0</v>
+      </c>
+      <c r="S143" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -8951,6 +9813,12 @@
       <c r="Q144" t="b">
         <v>0</v>
       </c>
+      <c r="R144" t="b">
+        <v>0</v>
+      </c>
+      <c r="S144" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -9010,6 +9878,12 @@
       <c r="Q145" t="b">
         <v>1</v>
       </c>
+      <c r="R145" t="b">
+        <v>0</v>
+      </c>
+      <c r="S145" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -9069,6 +9943,12 @@
       <c r="Q146" t="b">
         <v>0</v>
       </c>
+      <c r="R146" t="b">
+        <v>0</v>
+      </c>
+      <c r="S146" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -9128,6 +10008,12 @@
       <c r="Q147" t="b">
         <v>0</v>
       </c>
+      <c r="R147" t="b">
+        <v>0</v>
+      </c>
+      <c r="S147" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -9187,6 +10073,12 @@
       <c r="Q148" t="b">
         <v>0</v>
       </c>
+      <c r="R148" t="b">
+        <v>0</v>
+      </c>
+      <c r="S148" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -9246,6 +10138,12 @@
       <c r="Q149" t="b">
         <v>0</v>
       </c>
+      <c r="R149" t="b">
+        <v>0</v>
+      </c>
+      <c r="S149" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -9305,6 +10203,12 @@
       <c r="Q150" t="b">
         <v>0</v>
       </c>
+      <c r="R150" t="b">
+        <v>0</v>
+      </c>
+      <c r="S150" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -9364,6 +10268,12 @@
       <c r="Q151" t="b">
         <v>0</v>
       </c>
+      <c r="R151" t="b">
+        <v>0</v>
+      </c>
+      <c r="S151" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -9423,6 +10333,12 @@
       <c r="Q152" t="b">
         <v>0</v>
       </c>
+      <c r="R152" t="b">
+        <v>0</v>
+      </c>
+      <c r="S152" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -9482,6 +10398,12 @@
       <c r="Q153" t="b">
         <v>0</v>
       </c>
+      <c r="R153" t="b">
+        <v>0</v>
+      </c>
+      <c r="S153" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -9541,6 +10463,12 @@
       <c r="Q154" t="b">
         <v>0</v>
       </c>
+      <c r="R154" t="b">
+        <v>0</v>
+      </c>
+      <c r="S154" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -9600,6 +10528,12 @@
       <c r="Q155" t="b">
         <v>0</v>
       </c>
+      <c r="R155" t="b">
+        <v>0</v>
+      </c>
+      <c r="S155" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -9659,6 +10593,12 @@
       <c r="Q156" t="b">
         <v>0</v>
       </c>
+      <c r="R156" t="b">
+        <v>0</v>
+      </c>
+      <c r="S156" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -9718,6 +10658,12 @@
       <c r="Q157" t="b">
         <v>0</v>
       </c>
+      <c r="R157" t="b">
+        <v>0</v>
+      </c>
+      <c r="S157" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -9777,6 +10723,12 @@
       <c r="Q158" t="b">
         <v>0</v>
       </c>
+      <c r="R158" t="b">
+        <v>0</v>
+      </c>
+      <c r="S158" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -9836,6 +10788,12 @@
       <c r="Q159" t="b">
         <v>0</v>
       </c>
+      <c r="R159" t="b">
+        <v>0</v>
+      </c>
+      <c r="S159" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -9895,6 +10853,12 @@
       <c r="Q160" t="b">
         <v>0</v>
       </c>
+      <c r="R160" t="b">
+        <v>0</v>
+      </c>
+      <c r="S160" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -9954,6 +10918,12 @@
       <c r="Q161" t="b">
         <v>0</v>
       </c>
+      <c r="R161" t="b">
+        <v>0</v>
+      </c>
+      <c r="S161" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -10013,6 +10983,12 @@
       <c r="Q162" t="b">
         <v>0</v>
       </c>
+      <c r="R162" t="b">
+        <v>0</v>
+      </c>
+      <c r="S162" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -10072,6 +11048,12 @@
       <c r="Q163" t="b">
         <v>0</v>
       </c>
+      <c r="R163" t="b">
+        <v>0</v>
+      </c>
+      <c r="S163" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -10131,6 +11113,12 @@
       <c r="Q164" t="b">
         <v>0</v>
       </c>
+      <c r="R164" t="b">
+        <v>0</v>
+      </c>
+      <c r="S164" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -10190,6 +11178,12 @@
       <c r="Q165" t="b">
         <v>0</v>
       </c>
+      <c r="R165" t="b">
+        <v>0</v>
+      </c>
+      <c r="S165" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -10249,6 +11243,12 @@
       <c r="Q166" t="b">
         <v>0</v>
       </c>
+      <c r="R166" t="b">
+        <v>0</v>
+      </c>
+      <c r="S166" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -10308,6 +11308,12 @@
       <c r="Q167" t="b">
         <v>0</v>
       </c>
+      <c r="R167" t="b">
+        <v>0</v>
+      </c>
+      <c r="S167" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -10367,6 +11373,12 @@
       <c r="Q168" t="b">
         <v>0</v>
       </c>
+      <c r="R168" t="b">
+        <v>0</v>
+      </c>
+      <c r="S168" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -10426,6 +11438,12 @@
       <c r="Q169" t="b">
         <v>1</v>
       </c>
+      <c r="R169" t="b">
+        <v>0</v>
+      </c>
+      <c r="S169" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -10485,6 +11503,12 @@
       <c r="Q170" t="b">
         <v>0</v>
       </c>
+      <c r="R170" t="b">
+        <v>0</v>
+      </c>
+      <c r="S170" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -10544,6 +11568,12 @@
       <c r="Q171" t="b">
         <v>1</v>
       </c>
+      <c r="R171" t="b">
+        <v>0</v>
+      </c>
+      <c r="S171" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -10603,6 +11633,12 @@
       <c r="Q172" t="b">
         <v>0</v>
       </c>
+      <c r="R172" t="b">
+        <v>0</v>
+      </c>
+      <c r="S172" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -10660,6 +11696,12 @@
         <v>0</v>
       </c>
       <c r="Q173" t="b">
+        <v>0</v>
+      </c>
+      <c r="R173" t="b">
+        <v>0</v>
+      </c>
+      <c r="S173" t="b">
         <v>0</v>
       </c>
     </row>
